--- a/assets/data/excel/levelUp.xlsx
+++ b/assets/data/excel/levelUp.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,11 @@
           <t>unlockContent</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>upgradeCostBase</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -496,6 +501,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -516,6 +526,11 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>解锁内容描述</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>升级消耗基础值(菌丝)</t>
         </is>
       </c>
     </row>
@@ -534,6 +549,9 @@
           <t>初始觉醒，获得基础融合姬</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -545,7 +563,9 @@
       <c r="C5" t="n">
         <v>92</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,7 +577,9 @@
       <c r="C6" t="n">
         <v>191</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -569,7 +591,9 @@
       <c r="C7" t="n">
         <v>296</v>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -586,6 +610,9 @@
           <t>解锁每日辐射区探索</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -597,7 +624,9 @@
       <c r="C9" t="n">
         <v>526</v>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -609,7 +638,9 @@
       <c r="C10" t="n">
         <v>650</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -621,7 +652,9 @@
       <c r="C11" t="n">
         <v>781</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -633,7 +666,9 @@
       <c r="C12" t="n">
         <v>918</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -650,6 +685,9 @@
           <t>解锁装备强化系统</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -666,6 +704,9 @@
           <t>新地图解锁：废弃矿区(ZONE_MINE)</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -677,7 +718,9 @@
       <c r="C15" t="n">
         <v>1311</v>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -689,7 +732,9 @@
       <c r="C16" t="n">
         <v>1484</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -701,7 +746,9 @@
       <c r="C17" t="n">
         <v>1668</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -718,6 +765,9 @@
           <t>解锁融合姬突破系统</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -729,7 +779,9 @@
       <c r="C19" t="n">
         <v>2071</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -741,7 +793,9 @@
       <c r="C20" t="n">
         <v>2289</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -753,7 +807,9 @@
       <c r="C21" t="n">
         <v>2518</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -765,7 +821,9 @@
       <c r="C22" t="n">
         <v>2758</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -782,6 +840,9 @@
           <t>解锁竞技场</t>
         </is>
       </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -798,6 +859,9 @@
           <t>新地图解锁：沉没水城(ZONE_AQUA)</t>
         </is>
       </c>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -809,7 +873,9 @@
       <c r="C25" t="n">
         <v>3345</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -821,7 +887,9 @@
       <c r="C26" t="n">
         <v>3593</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -833,7 +901,9 @@
       <c r="C27" t="n">
         <v>3857</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -850,6 +920,9 @@
           <t>解锁芯片镶嵌系统</t>
         </is>
       </c>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -861,7 +934,9 @@
       <c r="C29" t="n">
         <v>4433</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -873,7 +948,9 @@
       <c r="C30" t="n">
         <v>4745</v>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -885,7 +962,9 @@
       <c r="C31" t="n">
         <v>5073</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -897,7 +976,9 @@
       <c r="C32" t="n">
         <v>5417</v>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -914,6 +995,9 @@
           <t>解锁公会系统</t>
         </is>
       </c>
+      <c r="E33" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -930,6 +1014,9 @@
           <t>新地图解锁：腐化丛林(ZONE_TREE)</t>
         </is>
       </c>
+      <c r="E34" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -941,7 +1028,9 @@
       <c r="C35" t="n">
         <v>6198</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -953,7 +1042,9 @@
       <c r="C36" t="n">
         <v>6520</v>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -965,7 +1056,9 @@
       <c r="C37" t="n">
         <v>6863</v>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -982,6 +1075,9 @@
           <t>解锁融合姬觉醒任务</t>
         </is>
       </c>
+      <c r="E38" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -993,7 +1089,9 @@
       <c r="C39" t="n">
         <v>7611</v>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1005,7 +1103,9 @@
       <c r="C40" t="n">
         <v>8016</v>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1017,7 +1117,9 @@
       <c r="C41" t="n">
         <v>8442</v>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1029,7 +1131,9 @@
       <c r="C42" t="n">
         <v>8889</v>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1046,6 +1150,9 @@
           <t>解锁深渊副本</t>
         </is>
       </c>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1062,6 +1169,9 @@
           <t>新地图解锁：深海遗迹(ZONE_DEEP)</t>
         </is>
       </c>
+      <c r="E44" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1073,7 +1183,9 @@
       <c r="C45" t="n">
         <v>9865</v>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1085,7 +1197,9 @@
       <c r="C46" t="n">
         <v>10261</v>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1097,7 +1211,9 @@
       <c r="C47" t="n">
         <v>10683</v>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1114,6 +1230,9 @@
           <t>解锁源核商店高级兑换</t>
         </is>
       </c>
+      <c r="E48" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1125,7 +1244,9 @@
       <c r="C49" t="n">
         <v>11604</v>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1137,7 +1258,9 @@
       <c r="C50" t="n">
         <v>12103</v>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1149,7 +1272,9 @@
       <c r="C51" t="n">
         <v>12627</v>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1161,7 +1286,9 @@
       <c r="C52" t="n">
         <v>13177</v>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1178,6 +1305,9 @@
           <t>解锁跨服竞技</t>
         </is>
       </c>
+      <c r="E53" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1194,6 +1324,9 @@
           <t>新地图解锁：军事要塞(ZONE_HQ)</t>
         </is>
       </c>
+      <c r="E54" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1205,7 +1338,9 @@
       <c r="C55" t="n">
         <v>14347</v>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1217,7 +1352,9 @@
       <c r="C56" t="n">
         <v>14818</v>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1229,7 +1366,9 @@
       <c r="C57" t="n">
         <v>15319</v>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1246,6 +1385,9 @@
           <t>解锁传说装备锻造</t>
         </is>
       </c>
+      <c r="E58" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1257,7 +1399,9 @@
       <c r="C59" t="n">
         <v>16413</v>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1269,7 +1413,9 @@
       <c r="C60" t="n">
         <v>17005</v>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1281,7 +1427,9 @@
       <c r="C61" t="n">
         <v>17628</v>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1293,7 +1441,9 @@
       <c r="C62" t="n">
         <v>18281</v>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1310,6 +1460,9 @@
           <t>解锁赛季挑战</t>
         </is>
       </c>
+      <c r="E63" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1326,6 +1479,9 @@
           <t>新地图解锁：荧光温泉(ZONE_SPRING)</t>
         </is>
       </c>
+      <c r="E64" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1337,7 +1493,9 @@
       <c r="C65" t="n">
         <v>19646</v>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1349,7 +1507,9 @@
       <c r="C66" t="n">
         <v>20191</v>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1361,7 +1521,9 @@
       <c r="C67" t="n">
         <v>20771</v>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1378,6 +1540,9 @@
           <t>解锁融合姬终极进化</t>
         </is>
       </c>
+      <c r="E68" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1389,7 +1554,9 @@
       <c r="C69" t="n">
         <v>22038</v>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1401,7 +1568,9 @@
       <c r="C70" t="n">
         <v>22724</v>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1413,7 +1582,9 @@
       <c r="C71" t="n">
         <v>23445</v>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1425,7 +1596,9 @@
       <c r="C72" t="n">
         <v>24201</v>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1442,6 +1615,9 @@
           <t>解锁世界Boss</t>
         </is>
       </c>
+      <c r="E73" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1458,6 +1634,9 @@
           <t>新地图解锁：机械军火库(ZONE_ARSENAL)</t>
         </is>
       </c>
+      <c r="E74" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1469,7 +1648,9 @@
       <c r="C75" t="n">
         <v>25761</v>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1481,7 +1662,9 @@
       <c r="C76" t="n">
         <v>26381</v>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1493,7 +1676,9 @@
       <c r="C77" t="n">
         <v>27041</v>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1510,6 +1695,9 @@
           <t>解锁传说级融合姬召唤</t>
         </is>
       </c>
+      <c r="E78" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1521,7 +1709,9 @@
       <c r="C79" t="n">
         <v>28481</v>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1533,7 +1723,9 @@
       <c r="C80" t="n">
         <v>29261</v>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1545,7 +1737,9 @@
       <c r="C81" t="n">
         <v>30081</v>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1557,7 +1751,9 @@
       <c r="C82" t="n">
         <v>30941</v>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1574,6 +1770,9 @@
           <t>解锁终局副本</t>
         </is>
       </c>
+      <c r="E83" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1590,6 +1789,9 @@
           <t>新地图解锁：方舟核心(ZONE_CORE)</t>
         </is>
       </c>
+      <c r="E84" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1601,7 +1803,9 @@
       <c r="C85" t="n">
         <v>32694</v>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1613,7 +1817,9 @@
       <c r="C86" t="n">
         <v>33388</v>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1625,7 +1831,9 @@
       <c r="C87" t="n">
         <v>34127</v>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1642,6 +1850,9 @@
           <t>解锁UR品质装备掉落</t>
         </is>
       </c>
+      <c r="E88" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1653,7 +1864,9 @@
       <c r="C89" t="n">
         <v>35739</v>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1665,7 +1878,9 @@
       <c r="C90" t="n">
         <v>36612</v>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1677,7 +1892,9 @@
       <c r="C91" t="n">
         <v>37530</v>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1689,7 +1906,9 @@
       <c r="C92" t="n">
         <v>38493</v>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1706,6 +1925,9 @@
           <t>解锁辐射风暴(ZONE_STORM)</t>
         </is>
       </c>
+      <c r="E93" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1722,6 +1944,9 @@
           <t>新地图解锁：终焉之地(ZONE_OMEGA)</t>
         </is>
       </c>
+      <c r="E94" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1733,7 +1958,9 @@
       <c r="C95" t="n">
         <v>40441</v>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1745,7 +1972,9 @@
       <c r="C96" t="n">
         <v>41209</v>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1757,7 +1986,9 @@
       <c r="C97" t="n">
         <v>42027</v>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1774,6 +2005,9 @@
           <t>解锁LE品质融合姬碎片</t>
         </is>
       </c>
+      <c r="E98" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1785,7 +2019,9 @@
       <c r="C99" t="n">
         <v>43812</v>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1797,7 +2033,9 @@
       <c r="C100" t="n">
         <v>44779</v>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1809,7 +2047,9 @@
       <c r="C101" t="n">
         <v>45795</v>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -1825,6 +2065,9 @@
         <is>
           <t>达到满级，解锁全内容</t>
         </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/excel/levelUp.xlsx
+++ b/assets/data/excel/levelUp.xlsx
@@ -564,7 +564,7 @@
         <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         <v>191</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -592,7 +592,7 @@
         <v>296</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>526</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -639,7 +639,7 @@
         <v>650</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         <v>781</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -667,7 +667,7 @@
         <v>918</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -719,7 +719,7 @@
         <v>1311</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
@@ -733,7 +733,7 @@
         <v>1484</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17">
@@ -747,7 +747,7 @@
         <v>1668</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19">
@@ -780,7 +780,7 @@
         <v>2071</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20">
@@ -794,7 +794,7 @@
         <v>2289</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21">
@@ -808,7 +808,7 @@
         <v>2518</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         <v>2758</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25">
@@ -874,7 +874,7 @@
         <v>3345</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26">
@@ -888,7 +888,7 @@
         <v>3593</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
@@ -902,7 +902,7 @@
         <v>3857</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29">
@@ -935,7 +935,7 @@
         <v>4433</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30">
@@ -949,7 +949,7 @@
         <v>4745</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31">
@@ -963,7 +963,7 @@
         <v>5073</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32">
@@ -977,7 +977,7 @@
         <v>5417</v>
       </c>
       <c r="E32" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35">
@@ -1029,7 +1029,7 @@
         <v>6198</v>
       </c>
       <c r="E35" t="n">
-        <v>100</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36">
@@ -1043,7 +1043,7 @@
         <v>6520</v>
       </c>
       <c r="E36" t="n">
-        <v>100</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37">
@@ -1057,7 +1057,7 @@
         <v>6863</v>
       </c>
       <c r="E37" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39">
@@ -1090,7 +1090,7 @@
         <v>7611</v>
       </c>
       <c r="E39" t="n">
-        <v>100</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40">
@@ -1104,7 +1104,7 @@
         <v>8016</v>
       </c>
       <c r="E40" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41">
@@ -1118,7 +1118,7 @@
         <v>8442</v>
       </c>
       <c r="E41" t="n">
-        <v>100</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42">
@@ -1132,7 +1132,7 @@
         <v>8889</v>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45">
@@ -1184,7 +1184,7 @@
         <v>9865</v>
       </c>
       <c r="E45" t="n">
-        <v>100</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46">
@@ -1198,7 +1198,7 @@
         <v>10261</v>
       </c>
       <c r="E46" t="n">
-        <v>100</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47">
@@ -1212,7 +1212,7 @@
         <v>10683</v>
       </c>
       <c r="E47" t="n">
-        <v>100</v>
+        <v>315</v>
       </c>
     </row>
     <row r="48">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49">
@@ -1245,7 +1245,7 @@
         <v>11604</v>
       </c>
       <c r="E49" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
     </row>
     <row r="50">
@@ -1259,7 +1259,7 @@
         <v>12103</v>
       </c>
       <c r="E50" t="n">
-        <v>100</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51">
@@ -1273,7 +1273,7 @@
         <v>12627</v>
       </c>
       <c r="E51" t="n">
-        <v>100</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52">
@@ -1287,7 +1287,7 @@
         <v>13177</v>
       </c>
       <c r="E52" t="n">
-        <v>100</v>
+        <v>340</v>
       </c>
     </row>
     <row r="53">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100</v>
+        <v>345</v>
       </c>
     </row>
     <row r="54">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
     </row>
     <row r="55">
@@ -1339,7 +1339,7 @@
         <v>14347</v>
       </c>
       <c r="E55" t="n">
-        <v>100</v>
+        <v>355</v>
       </c>
     </row>
     <row r="56">
@@ -1353,7 +1353,7 @@
         <v>14818</v>
       </c>
       <c r="E56" t="n">
-        <v>100</v>
+        <v>360</v>
       </c>
     </row>
     <row r="57">
@@ -1367,7 +1367,7 @@
         <v>15319</v>
       </c>
       <c r="E57" t="n">
-        <v>100</v>
+        <v>365</v>
       </c>
     </row>
     <row r="58">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100</v>
+        <v>370</v>
       </c>
     </row>
     <row r="59">
@@ -1400,7 +1400,7 @@
         <v>16413</v>
       </c>
       <c r="E59" t="n">
-        <v>100</v>
+        <v>375</v>
       </c>
     </row>
     <row r="60">
@@ -1414,7 +1414,7 @@
         <v>17005</v>
       </c>
       <c r="E60" t="n">
-        <v>100</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61">
@@ -1428,7 +1428,7 @@
         <v>17628</v>
       </c>
       <c r="E61" t="n">
-        <v>100</v>
+        <v>385</v>
       </c>
     </row>
     <row r="62">
@@ -1442,7 +1442,7 @@
         <v>18281</v>
       </c>
       <c r="E62" t="n">
-        <v>100</v>
+        <v>390</v>
       </c>
     </row>
     <row r="63">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65">
@@ -1494,7 +1494,7 @@
         <v>19646</v>
       </c>
       <c r="E65" t="n">
-        <v>100</v>
+        <v>405</v>
       </c>
     </row>
     <row r="66">
@@ -1508,7 +1508,7 @@
         <v>20191</v>
       </c>
       <c r="E66" t="n">
-        <v>100</v>
+        <v>410</v>
       </c>
     </row>
     <row r="67">
@@ -1522,7 +1522,7 @@
         <v>20771</v>
       </c>
       <c r="E67" t="n">
-        <v>100</v>
+        <v>415</v>
       </c>
     </row>
     <row r="68">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100</v>
+        <v>420</v>
       </c>
     </row>
     <row r="69">
@@ -1555,7 +1555,7 @@
         <v>22038</v>
       </c>
       <c r="E69" t="n">
-        <v>100</v>
+        <v>425</v>
       </c>
     </row>
     <row r="70">
@@ -1569,7 +1569,7 @@
         <v>22724</v>
       </c>
       <c r="E70" t="n">
-        <v>100</v>
+        <v>430</v>
       </c>
     </row>
     <row r="71">
@@ -1583,7 +1583,7 @@
         <v>23445</v>
       </c>
       <c r="E71" t="n">
-        <v>100</v>
+        <v>435</v>
       </c>
     </row>
     <row r="72">
@@ -1597,7 +1597,7 @@
         <v>24201</v>
       </c>
       <c r="E72" t="n">
-        <v>100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="73">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100</v>
+        <v>445</v>
       </c>
     </row>
     <row r="74">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
     </row>
     <row r="75">
@@ -1649,7 +1649,7 @@
         <v>25761</v>
       </c>
       <c r="E75" t="n">
-        <v>100</v>
+        <v>455</v>
       </c>
     </row>
     <row r="76">
@@ -1663,7 +1663,7 @@
         <v>26381</v>
       </c>
       <c r="E76" t="n">
-        <v>100</v>
+        <v>460</v>
       </c>
     </row>
     <row r="77">
@@ -1677,7 +1677,7 @@
         <v>27041</v>
       </c>
       <c r="E77" t="n">
-        <v>100</v>
+        <v>465</v>
       </c>
     </row>
     <row r="78">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100</v>
+        <v>470</v>
       </c>
     </row>
     <row r="79">
@@ -1710,7 +1710,7 @@
         <v>28481</v>
       </c>
       <c r="E79" t="n">
-        <v>100</v>
+        <v>475</v>
       </c>
     </row>
     <row r="80">
@@ -1724,7 +1724,7 @@
         <v>29261</v>
       </c>
       <c r="E80" t="n">
-        <v>100</v>
+        <v>480</v>
       </c>
     </row>
     <row r="81">
@@ -1738,7 +1738,7 @@
         <v>30081</v>
       </c>
       <c r="E81" t="n">
-        <v>100</v>
+        <v>485</v>
       </c>
     </row>
     <row r="82">
@@ -1752,7 +1752,7 @@
         <v>30941</v>
       </c>
       <c r="E82" t="n">
-        <v>100</v>
+        <v>490</v>
       </c>
     </row>
     <row r="83">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100</v>
+        <v>495</v>
       </c>
     </row>
     <row r="84">
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85">
@@ -1804,7 +1804,7 @@
         <v>32694</v>
       </c>
       <c r="E85" t="n">
-        <v>100</v>
+        <v>505</v>
       </c>
     </row>
     <row r="86">
@@ -1818,7 +1818,7 @@
         <v>33388</v>
       </c>
       <c r="E86" t="n">
-        <v>100</v>
+        <v>510</v>
       </c>
     </row>
     <row r="87">
@@ -1832,7 +1832,7 @@
         <v>34127</v>
       </c>
       <c r="E87" t="n">
-        <v>100</v>
+        <v>515</v>
       </c>
     </row>
     <row r="88">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="89">
@@ -1865,7 +1865,7 @@
         <v>35739</v>
       </c>
       <c r="E89" t="n">
-        <v>100</v>
+        <v>525</v>
       </c>
     </row>
     <row r="90">
@@ -1879,7 +1879,7 @@
         <v>36612</v>
       </c>
       <c r="E90" t="n">
-        <v>100</v>
+        <v>530</v>
       </c>
     </row>
     <row r="91">
@@ -1893,7 +1893,7 @@
         <v>37530</v>
       </c>
       <c r="E91" t="n">
-        <v>100</v>
+        <v>535</v>
       </c>
     </row>
     <row r="92">
@@ -1907,7 +1907,7 @@
         <v>38493</v>
       </c>
       <c r="E92" t="n">
-        <v>100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="93">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100</v>
+        <v>545</v>
       </c>
     </row>
     <row r="94">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100</v>
+        <v>550</v>
       </c>
     </row>
     <row r="95">
@@ -1959,7 +1959,7 @@
         <v>40441</v>
       </c>
       <c r="E95" t="n">
-        <v>100</v>
+        <v>555</v>
       </c>
     </row>
     <row r="96">
@@ -1973,7 +1973,7 @@
         <v>41209</v>
       </c>
       <c r="E96" t="n">
-        <v>100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="97">
@@ -1987,7 +1987,7 @@
         <v>42027</v>
       </c>
       <c r="E97" t="n">
-        <v>100</v>
+        <v>565</v>
       </c>
     </row>
     <row r="98">
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100</v>
+        <v>570</v>
       </c>
     </row>
     <row r="99">
@@ -2020,7 +2020,7 @@
         <v>43812</v>
       </c>
       <c r="E99" t="n">
-        <v>100</v>
+        <v>575</v>
       </c>
     </row>
     <row r="100">
@@ -2034,7 +2034,7 @@
         <v>44779</v>
       </c>
       <c r="E100" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
     </row>
     <row r="101">
@@ -2048,7 +2048,7 @@
         <v>45795</v>
       </c>
       <c r="E101" t="n">
-        <v>100</v>
+        <v>585</v>
       </c>
     </row>
     <row r="102">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
